--- a/Notes/datamapping-TMHM(2).xlsx
+++ b/Notes/datamapping-TMHM(2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735887DF-B608-453B-A910-076FA178EA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AA15A1-2BE9-45A8-958E-F69601D9BBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{181C1671-B665-4720-840A-95B497A76B28}"/>
+    <workbookView xWindow="13320" yWindow="0" windowWidth="15585" windowHeight="15585" activeTab="1" xr2:uid="{181C1671-B665-4720-840A-95B497A76B28}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="395">
   <si>
     <t>TM01</t>
   </si>
@@ -1221,6 +1221,9 @@
   </si>
   <si>
     <t>tmhm FLASH, TOXIC, BULLET_SEED, HIDDEN_POWER, PROTECT, ENDURE, GIGA_DRAIN, SOLARBEAM, MUD_SLAP, DOUBLE_TEAM, REST, SUBSTITUTE, ENERGY_BALL, ROCK_SMASH, HEADBUTT, DOUBLE_EDGE, CURSE, SLUDGE_BOMB, SWAGGER, ATTRACT, SWORDS_DANCE, SUNNY_DAY, SNORE, SLEEP_TALK, SWEET_SCENT</t>
+  </si>
+  <si>
+    <t>SHARPEN</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1419,12 +1422,11 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1506,36 +1508,6 @@
       <font>
         <color rgb="FF00B050"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4766,7 +4738,7 @@
         <v>164</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>167</v>
+        <v>394</v>
       </c>
       <c r="L46" t="s">
         <v>347</v>
@@ -5505,11 +5477,11 @@
   <conditionalFormatting sqref="G1:G62 G64:G68 G70:G1048576 B1:B1048576">
     <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K68 K70:K87 K97:K1048576 K89:K95">
+    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K68 K70:K87 K97:K1048576 K89:K95">
-    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5535,7 +5507,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5546,488 +5518,488 @@
   <dimension ref="A2:A95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="31" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="2" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="2" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="2" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="2" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="2" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="2" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="2" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="2" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="2" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="2" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="2" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="2" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="2" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="2" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
+      <c r="A43" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="2" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="2" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
+      <c r="A46" s="2" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="2" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="2" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="31" t="s">
+      <c r="A49" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="2" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="2" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="31" t="s">
+      <c r="A52" s="2" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="2" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="31" t="s">
+      <c r="A55" s="2" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="2" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="31" t="s">
+      <c r="A57" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="31" t="s">
+      <c r="A58" s="2" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="31" t="s">
+      <c r="A59" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="31" t="s">
+      <c r="A60" s="2" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="31" t="s">
+      <c r="A61" s="2" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="31" t="s">
+      <c r="A62" s="2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="31" t="s">
+      <c r="A63" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="31" t="s">
+      <c r="A64" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="31" t="s">
+      <c r="A65" s="2" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="31" t="s">
+      <c r="A66" s="2" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="31" t="s">
+      <c r="A67" s="2" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="31" t="s">
+      <c r="A68" s="2" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="31" t="s">
+      <c r="A69" s="2" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="31" t="s">
+      <c r="A70" s="2" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="31" t="s">
+      <c r="A71" s="2" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="31" t="s">
+      <c r="A72" s="2" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="31" t="s">
+      <c r="A73" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="31" t="s">
+      <c r="A74" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="31" t="s">
+      <c r="A75" s="2" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="31" t="s">
+      <c r="A76" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="31" t="s">
+      <c r="A77" s="2" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="31" t="s">
+      <c r="A78" s="2" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="31" t="s">
+      <c r="A79" s="2" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="31" t="s">
+      <c r="A80" s="2" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="31" t="s">
+      <c r="A81" s="2" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="31" t="s">
+      <c r="A82" s="2" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="31" t="s">
+      <c r="A83" s="2" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="31" t="s">
+      <c r="A84" s="2" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="31" t="s">
+      <c r="A85" s="2" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="31" t="s">
+      <c r="A86" s="2" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="31" t="s">
+      <c r="A87" s="2" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="31" t="s">
+      <c r="A88" s="2" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="31" t="s">
+      <c r="A89" s="2" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="31" t="s">
+      <c r="A90" s="2" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="31" t="s">
+      <c r="A91" s="2" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="31" t="s">
+      <c r="A92" s="2" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="31" t="s">
+      <c r="A93" s="2" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="31" t="s">
+      <c r="A94" s="2" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="31" t="s">
+      <c r="A95" s="2" t="s">
         <v>380</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G44">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  <conditionalFormatting sqref="A2:A69 A71:A88 A111:A1048576 A90:A96">
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:C1 A25:C1048576 A2:B24">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A69 A71:A88 A111:A1048576 A90:A96">
-    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
+  <conditionalFormatting sqref="G44">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Notes/datamapping-TMHM(2).xlsx
+++ b/Notes/datamapping-TMHM(2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AA15A1-2BE9-45A8-958E-F69601D9BBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4C8D23-41EC-4481-BFFF-0BFAA1EFFDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13320" yWindow="0" windowWidth="15585" windowHeight="15585" activeTab="1" xr2:uid="{181C1671-B665-4720-840A-95B497A76B28}"/>
+    <workbookView xWindow="10515" yWindow="0" windowWidth="18390" windowHeight="15585" activeTab="1" xr2:uid="{181C1671-B665-4720-840A-95B497A76B28}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="396">
   <si>
     <t>TM01</t>
   </si>
@@ -1224,13 +1224,16 @@
   </si>
   <si>
     <t>SHARPEN</t>
+  </si>
+  <si>
+    <t>unused</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1327,6 +1330,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1390,7 +1409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1422,6 +1441,8 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1846,7 +1867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A586E0-AA82-4B61-856B-EF239FAD6E4E}">
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -1860,6 +1881,7 @@
     <col min="9" max="9" width="1.7109375" customWidth="1"/>
     <col min="10" max="10" width="5.7109375" customWidth="1"/>
     <col min="11" max="11" width="16.7109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2876,7 +2898,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>176</v>
       </c>
@@ -2896,7 +2918,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>180</v>
       </c>
@@ -2916,7 +2938,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G51" t="s">
         <v>184</v>
       </c>
@@ -2930,7 +2952,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G52" t="s">
         <v>186</v>
       </c>
@@ -2944,7 +2966,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G53" t="s">
         <v>188</v>
       </c>
@@ -2958,7 +2980,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E54" t="s">
         <v>190</v>
       </c>
@@ -2969,7 +2991,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G55" t="s">
         <v>192</v>
       </c>
@@ -2977,7 +2999,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G56" t="s">
         <v>194</v>
       </c>
@@ -2985,7 +3007,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G57" t="s">
         <v>196</v>
       </c>
@@ -2993,7 +3015,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G58" t="s">
         <v>198</v>
       </c>
@@ -3001,7 +3023,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G59" t="s">
         <v>200</v>
       </c>
@@ -3015,21 +3037,27 @@
         <v>201</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G60" t="s">
         <v>202</v>
       </c>
       <c r="H60" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="J60" t="s">
+        <v>252</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="L60" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="M60" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="J60" t="s">
-        <v>202</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G61" t="s">
         <v>204</v>
       </c>
@@ -3037,7 +3065,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G62" t="s">
         <v>206</v>
       </c>
@@ -3045,7 +3073,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G63" t="s">
         <v>208</v>
       </c>
@@ -3053,7 +3081,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G64" t="s">
         <v>210</v>
       </c>
@@ -3286,13 +3314,7 @@
         <v>250</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="J85" t="s">
-        <v>252</v>
-      </c>
-      <c r="K85" s="6" t="s">
-        <v>251</v>
+        <v>395</v>
       </c>
     </row>
     <row r="86" spans="4:11" x14ac:dyDescent="0.25">
@@ -4632,7 +4654,7 @@
       <c r="B43" t="s">
         <v>154</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="15" t="s">
         <v>277</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -5082,10 +5104,10 @@
         <v>202</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="L60" t="s">
-        <v>277</v>
+        <v>251</v>
+      </c>
+      <c r="L60" s="26" t="s">
+        <v>377</v>
       </c>
       <c r="M60" s="18"/>
     </row>
@@ -5364,12 +5386,6 @@
     <row r="85" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J85" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="K85" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="L85" s="26" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="86" spans="7:13" x14ac:dyDescent="0.25">
@@ -5474,10 +5490,10 @@
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G62 G64:G68 G70:G1048576 B1:B1048576">
+  <conditionalFormatting sqref="G1:G59 G61:G62 G64:G68 G70:G1048576 B1:B1048576">
     <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K68 K70:K87 K97:K1048576 K89:K95">
+  <conditionalFormatting sqref="K1:K68 K70:K84 K86:K87 K97:K1048576 K89:K95">
     <cfRule type="duplicateValues" dxfId="5" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">

--- a/Notes/datamapping-TMHM(2).xlsx
+++ b/Notes/datamapping-TMHM(2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4C8D23-41EC-4481-BFFF-0BFAA1EFFDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5D87CA-8C0D-4B72-8A81-C895A1ECC88D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10515" yWindow="0" windowWidth="18390" windowHeight="15585" activeTab="1" xr2:uid="{181C1671-B665-4720-840A-95B497A76B28}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{181C1671-B665-4720-840A-95B497A76B28}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="397">
   <si>
     <t>TM01</t>
   </si>
@@ -1226,7 +1226,10 @@
     <t>SHARPEN</t>
   </si>
   <si>
-    <t>unused</t>
+    <t>SILVER_WIND</t>
+  </si>
+  <si>
+    <t>?victory road?</t>
   </si>
 </sst>
 </file>
@@ -1409,7 +1412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1443,6 +1446,7 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3069,8 +3073,14 @@
       <c r="G62" t="s">
         <v>206</v>
       </c>
-      <c r="H62" s="2" t="s">
-        <v>207</v>
+      <c r="H62" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="J62" t="s">
+        <v>206</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -3313,8 +3323,8 @@
       <c r="G85" t="s">
         <v>250</v>
       </c>
-      <c r="H85" s="3" t="s">
-        <v>395</v>
+      <c r="H85" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="4:11" x14ac:dyDescent="0.25">
@@ -3333,7 +3343,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H1:H68 H70:H1048576 E91:E1048576 E1:E88 B1:B1048576">
+  <conditionalFormatting sqref="H1:H61 H63:H68 H70:H1048576 E91:E1048576 E1:E88 B1:B1048576">
     <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3343,7 +3353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF01332C-EC16-49E6-9CB3-0253CF8F9BDE}">
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -5123,14 +5133,14 @@
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J62" t="s">
+      <c r="J62" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="K62" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="L62" s="26" t="s">
-        <v>372</v>
+      <c r="K62" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="L62" s="15" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -5158,7 +5168,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="65" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J65" s="3" t="s">
         <v>212</v>
       </c>
@@ -5169,7 +5179,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="66" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J66" t="s">
         <v>214</v>
       </c>
@@ -5180,7 +5190,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="67" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J67" t="s">
         <v>216</v>
       </c>
@@ -5191,7 +5201,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="68" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J68" s="3" t="s">
         <v>218</v>
       </c>
@@ -5202,18 +5212,19 @@
         <v>337</v>
       </c>
     </row>
-    <row r="69" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H69" s="33"/>
       <c r="J69" t="s">
         <v>220</v>
       </c>
-      <c r="K69" s="3" t="s">
-        <v>390</v>
+      <c r="K69" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="L69" s="26" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="70" spans="10:13" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="70" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J70" t="s">
         <v>221</v>
       </c>
@@ -5224,7 +5235,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="71" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J71" s="3" t="s">
         <v>222</v>
       </c>
@@ -5235,7 +5246,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="72" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J72" t="s">
         <v>224</v>
       </c>
@@ -5246,7 +5257,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="73" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J73" t="s">
         <v>225</v>
       </c>
@@ -5257,7 +5268,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="74" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J74" s="3" t="s">
         <v>226</v>
       </c>
@@ -5268,7 +5279,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="75" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J75" t="s">
         <v>228</v>
       </c>
@@ -5280,7 +5291,7 @@
       </c>
       <c r="M75" s="18"/>
     </row>
-    <row r="76" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J76" t="s">
         <v>230</v>
       </c>
@@ -5292,7 +5303,7 @@
       </c>
       <c r="M76" s="18"/>
     </row>
-    <row r="77" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J77" t="s">
         <v>232</v>
       </c>
@@ -5304,7 +5315,7 @@
       </c>
       <c r="M77" s="18"/>
     </row>
-    <row r="78" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J78" t="s">
         <v>234</v>
       </c>
@@ -5316,7 +5327,7 @@
       </c>
       <c r="M78" s="18"/>
     </row>
-    <row r="79" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J79" s="3" t="s">
         <v>236</v>
       </c>
@@ -5327,7 +5338,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="80" spans="10:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J80" t="s">
         <v>238</v>
       </c>
@@ -5390,15 +5401,6 @@
     </row>
     <row r="86" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G86" s="2"/>
-      <c r="J86" t="s">
-        <v>387</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="L86" t="s">
-        <v>275</v>
-      </c>
     </row>
     <row r="87" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G87" s="7"/>
@@ -5406,10 +5408,10 @@
         <v>387</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L87" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="88" spans="7:13" x14ac:dyDescent="0.25">
@@ -5417,7 +5419,7 @@
         <v>387</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>152</v>
+        <v>383</v>
       </c>
       <c r="L88" t="s">
         <v>276</v>
@@ -5428,7 +5430,7 @@
         <v>387</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>384</v>
+        <v>152</v>
       </c>
       <c r="L89" t="s">
         <v>276</v>
@@ -5439,7 +5441,7 @@
         <v>387</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L90" t="s">
         <v>276</v>
@@ -5450,7 +5452,10 @@
         <v>387</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
+      </c>
+      <c r="L91" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="92" spans="7:13" x14ac:dyDescent="0.25">
@@ -5458,10 +5463,7 @@
         <v>387</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="L92" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="93" spans="7:13" x14ac:dyDescent="0.25">
@@ -5469,7 +5471,7 @@
         <v>387</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="L93" t="s">
         <v>391</v>
@@ -5480,9 +5482,20 @@
         <v>387</v>
       </c>
       <c r="K94" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="L94" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="95" spans="7:13" x14ac:dyDescent="0.25">
+      <c r="J95" t="s">
+        <v>387</v>
+      </c>
+      <c r="K95" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="L94" t="s">
+      <c r="L95" t="s">
         <v>391</v>
       </c>
     </row>
@@ -5490,16 +5503,17 @@
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G59 G61:G62 G64:G68 G70:G1048576 B1:B1048576">
+  <conditionalFormatting sqref="G1:G59 G61:G62 G64:G65 G67:G68 F66 G70:G1048576 B1:B1048576">
     <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K68 K70:K84 K86:K87 K97:K1048576 K89:K95">
-    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
+  <conditionalFormatting sqref="M1:M1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+  <conditionalFormatting sqref="K1:K61 K63:K84 K87:K88 K97:K1048576 K90:K95">
+    <cfRule type="duplicateValues" dxfId="4" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Notes/datamapping-TMHM(2).xlsx
+++ b/Notes/datamapping-TMHM(2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5D87CA-8C0D-4B72-8A81-C895A1ECC88D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F887D9-66B1-4DFE-BC22-9BF23092C43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{181C1671-B665-4720-840A-95B497A76B28}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="536">
   <si>
     <t>TM01</t>
   </si>
@@ -1145,9 +1145,6 @@
     <t>AZALEA GYM</t>
   </si>
   <si>
-    <t>route 28</t>
-  </si>
-  <si>
     <t>lavender town</t>
   </si>
   <si>
@@ -1157,21 +1154,9 @@
     <t>dark cave</t>
   </si>
   <si>
-    <t>lavender town / tower</t>
-  </si>
-  <si>
-    <t>copycat house?</t>
-  </si>
-  <si>
     <t>rock tunnel</t>
   </si>
   <si>
-    <t>safari zone (double team)</t>
-  </si>
-  <si>
-    <t>goldenrod dept store</t>
-  </si>
-  <si>
     <t>lighthouse / ice path</t>
   </si>
   <si>
@@ -1208,15 +1193,9 @@
     <t>VIOLET GYM</t>
   </si>
   <si>
-    <t>ilex forest or kanto?</t>
-  </si>
-  <si>
     <t>ROCK_POLISH</t>
   </si>
   <si>
-    <t>fighting dojo?</t>
-  </si>
-  <si>
     <t>bulbasaur</t>
   </si>
   <si>
@@ -1229,7 +1208,445 @@
     <t>SILVER_WIND</t>
   </si>
   <si>
-    <t>?victory road?</t>
+    <t>Tackle</t>
+  </si>
+  <si>
+    <t>Tail Whip</t>
+  </si>
+  <si>
+    <t>Helping Hand</t>
+  </si>
+  <si>
+    <t>Sand-attack</t>
+  </si>
+  <si>
+    <t>Quick Attack</t>
+  </si>
+  <si>
+    <t>Last Resort</t>
+  </si>
+  <si>
+    <t>Sunny Day</t>
+  </si>
+  <si>
+    <t>Hidden Power</t>
+  </si>
+  <si>
+    <t>Hyper Beam</t>
+  </si>
+  <si>
+    <t>Rain Dance</t>
+  </si>
+  <si>
+    <t>Iron Tail</t>
+  </si>
+  <si>
+    <t>Shadow Ball</t>
+  </si>
+  <si>
+    <t>Double Team</t>
+  </si>
+  <si>
+    <t>Facade</t>
+  </si>
+  <si>
+    <t>Secret Power</t>
+  </si>
+  <si>
+    <t>Attract</t>
+  </si>
+  <si>
+    <t>Giga Impact</t>
+  </si>
+  <si>
+    <t>Captivate</t>
+  </si>
+  <si>
+    <t>Sleep Talk</t>
+  </si>
+  <si>
+    <t>Natural Gift</t>
+  </si>
+  <si>
+    <t>Rock Smash</t>
+  </si>
+  <si>
+    <t>Mud-slap</t>
+  </si>
+  <si>
+    <t>Heal Bell</t>
+  </si>
+  <si>
+    <t>Charm</t>
+  </si>
+  <si>
+    <t>Flail</t>
+  </si>
+  <si>
+    <t>Tickle</t>
+  </si>
+  <si>
+    <t>Wish</t>
+  </si>
+  <si>
+    <t>Yawn</t>
+  </si>
+  <si>
+    <t>Fake Tears</t>
+  </si>
+  <si>
+    <t>Covet</t>
+  </si>
+  <si>
+    <t>Growl</t>
+  </si>
+  <si>
+    <t>Bite</t>
+  </si>
+  <si>
+    <t>Baton Pass</t>
+  </si>
+  <si>
+    <t>Take Down</t>
+  </si>
+  <si>
+    <t>Trump Card</t>
+  </si>
+  <si>
+    <t>Ice Beam</t>
+  </si>
+  <si>
+    <t>Water Pulse</t>
+  </si>
+  <si>
+    <t>DRAGON CLAW</t>
+  </si>
+  <si>
+    <t>CALM MIND</t>
+  </si>
+  <si>
+    <t>BULK UP</t>
+  </si>
+  <si>
+    <t>BODY SLAM</t>
+  </si>
+  <si>
+    <t>BULLET SEED</t>
+  </si>
+  <si>
+    <t>HIDDEN POWER</t>
+  </si>
+  <si>
+    <t>WATER GUN</t>
+  </si>
+  <si>
+    <t>ICE BEAM</t>
+  </si>
+  <si>
+    <t>HYPER BEAM</t>
+  </si>
+  <si>
+    <t>PAY DAY</t>
+  </si>
+  <si>
+    <t>SEISMIC TOSS</t>
+  </si>
+  <si>
+    <t>GIGA DRAIN</t>
+  </si>
+  <si>
+    <t>IRON TAIL</t>
+  </si>
+  <si>
+    <t>PSYCHIC M</t>
+  </si>
+  <si>
+    <t>WATER PULSE</t>
+  </si>
+  <si>
+    <t>DOUBLE TEAM</t>
+  </si>
+  <si>
+    <t>FIRE BLAST</t>
+  </si>
+  <si>
+    <t>AERIAL ACE</t>
+  </si>
+  <si>
+    <t>SKY ATTACK</t>
+  </si>
+  <si>
+    <t>THUNDER WAVE</t>
+  </si>
+  <si>
+    <t>ICY WIND</t>
+  </si>
+  <si>
+    <t>ROCK SLIDE</t>
+  </si>
+  <si>
+    <t>TRI ATTACK</t>
+  </si>
+  <si>
+    <t>FOCUS BLAST</t>
+  </si>
+  <si>
+    <t>ENERGY BALL</t>
+  </si>
+  <si>
+    <t>FALSE SWIPE</t>
+  </si>
+  <si>
+    <t>ROCK SMASH</t>
+  </si>
+  <si>
+    <t>AIR SLICE</t>
+  </si>
+  <si>
+    <t>DRAGON PULSE</t>
+  </si>
+  <si>
+    <t>FLASH CANNON</t>
+  </si>
+  <si>
+    <t>SILVER WIND</t>
+  </si>
+  <si>
+    <t>SLUDGE BOMB</t>
+  </si>
+  <si>
+    <t>SHADOW CLAW</t>
+  </si>
+  <si>
+    <t>STEEL WING</t>
+  </si>
+  <si>
+    <t>GIGA IMPACT</t>
+  </si>
+  <si>
+    <t>SHADOW BALL</t>
+  </si>
+  <si>
+    <t>STONE EDGE</t>
+  </si>
+  <si>
+    <t>GYRO BALL</t>
+  </si>
+  <si>
+    <t>SWORDS DANCE</t>
+  </si>
+  <si>
+    <t>SUNNY DAY</t>
+  </si>
+  <si>
+    <t>RAIN DANCE</t>
+  </si>
+  <si>
+    <t>DARK PULSE</t>
+  </si>
+  <si>
+    <t>POISON JAB</t>
+  </si>
+  <si>
+    <t>DREAM EATER</t>
+  </si>
+  <si>
+    <t>SLEEP TALK</t>
+  </si>
+  <si>
+    <t>SWEET SCENT</t>
+  </si>
+  <si>
+    <t>FIRE PUNCH</t>
+  </si>
+  <si>
+    <t>ICE PUNCH</t>
+  </si>
+  <si>
+    <t>DOUBLE-EDGE</t>
+  </si>
+  <si>
+    <t>MUD-SLAP</t>
+  </si>
+  <si>
+    <t>X-SCISSOR</t>
+  </si>
+  <si>
+    <t>Icy Wind</t>
+  </si>
+  <si>
+    <t>Ice Shard</t>
+  </si>
+  <si>
+    <t>Ice Fang</t>
+  </si>
+  <si>
+    <t>Mirror Coat</t>
+  </si>
+  <si>
+    <t>Hail</t>
+  </si>
+  <si>
+    <t>Barrier</t>
+  </si>
+  <si>
+    <t>Avalanche</t>
+  </si>
+  <si>
+    <t>Aqua Tail</t>
+  </si>
+  <si>
+    <t>Signal Beam</t>
+  </si>
+  <si>
+    <t>BRICK_BREAK</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>aa</t>
+  </si>
+  <si>
+    <t>ab</t>
+  </si>
+  <si>
+    <t>ac</t>
+  </si>
+  <si>
+    <t>ai</t>
+  </si>
+  <si>
+    <t>as</t>
+  </si>
+  <si>
+    <t>ad</t>
+  </si>
+  <si>
+    <t>ae</t>
+  </si>
+  <si>
+    <t>af</t>
+  </si>
+  <si>
+    <t>ag</t>
+  </si>
+  <si>
+    <t>ah</t>
+  </si>
+  <si>
+    <t>aj</t>
+  </si>
+  <si>
+    <t>ak</t>
+  </si>
+  <si>
+    <t>al</t>
+  </si>
+  <si>
+    <t>an</t>
+  </si>
+  <si>
+    <t>ao</t>
+  </si>
+  <si>
+    <t>ap</t>
+  </si>
+  <si>
+    <t>aq</t>
+  </si>
+  <si>
+    <t>ar</t>
+  </si>
+  <si>
+    <t>at</t>
+  </si>
+  <si>
+    <t>au</t>
+  </si>
+  <si>
+    <t>av</t>
+  </si>
+  <si>
+    <t>aw</t>
+  </si>
+  <si>
+    <t>ax</t>
+  </si>
+  <si>
+    <t>route 12 gate 2f</t>
+  </si>
+  <si>
+    <t>viridian forest (cut)</t>
+  </si>
+  <si>
+    <t>flower shop?</t>
+  </si>
+  <si>
+    <t>route 17</t>
+  </si>
+  <si>
+    <t>goldenrod dept</t>
+  </si>
+  <si>
+    <t>route 26</t>
+  </si>
+  <si>
+    <t>elsewhere?</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1767,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1399,6 +1816,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1412,7 +1835,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1446,12 +1869,13 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1464,11 +1888,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3074,13 +3508,13 @@
         <v>206</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="J62" t="s">
         <v>206</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -3148,13 +3582,13 @@
         <v>220</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="J69" t="s">
         <v>220</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="70" spans="7:11" x14ac:dyDescent="0.25">
@@ -3344,7 +3778,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1:H61 H63:H68 H70:H1048576 E91:E1048576 E1:E88 B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3380,7 +3814,7 @@
       <c r="C1" s="23" t="s">
         <v>259</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="15" t="s">
         <v>352</v>
       </c>
       <c r="F1" t="s">
@@ -3398,9 +3832,10 @@
       <c r="K1" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="L1" s="26" t="s">
+      <c r="L1" s="2" t="s">
         <v>360</v>
       </c>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3412,6 +3847,9 @@
       <c r="C2" s="20" t="s">
         <v>257</v>
       </c>
+      <c r="D2" s="15" t="s">
+        <v>355</v>
+      </c>
       <c r="F2" t="s">
         <v>3</v>
       </c>
@@ -3430,9 +3868,7 @@
       <c r="L2" t="s">
         <v>277</v>
       </c>
-      <c r="M2" t="s">
-        <v>359</v>
-      </c>
+      <c r="M2" s="33"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -3444,6 +3880,9 @@
       <c r="C3" s="18" t="s">
         <v>253</v>
       </c>
+      <c r="D3" s="15" t="s">
+        <v>356</v>
+      </c>
       <c r="F3" t="s">
         <v>7</v>
       </c>
@@ -3462,7 +3901,7 @@
       <c r="L3" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="M3" s="18"/>
+      <c r="M3" s="33"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -3474,6 +3913,9 @@
       <c r="C4" s="18" t="s">
         <v>254</v>
       </c>
+      <c r="D4" s="15" t="s">
+        <v>353</v>
+      </c>
       <c r="F4" t="s">
         <v>12</v>
       </c>
@@ -3492,7 +3934,7 @@
       <c r="L4" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="M4" s="18"/>
+      <c r="M4" s="33"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -3505,7 +3947,7 @@
         <v>277</v>
       </c>
       <c r="D5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -3525,7 +3967,7 @@
       <c r="L5" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="M5" s="18"/>
+      <c r="M5" s="33"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -3537,6 +3979,9 @@
       <c r="C6" s="19" t="s">
         <v>255</v>
       </c>
+      <c r="D6" s="15" t="s">
+        <v>354</v>
+      </c>
       <c r="F6" t="s">
         <v>21</v>
       </c>
@@ -3555,7 +4000,9 @@
       <c r="L6" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="M6" s="18"/>
+      <c r="M6" s="33" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -3567,6 +4014,9 @@
       <c r="C7" s="20" t="s">
         <v>257</v>
       </c>
+      <c r="D7" s="15" t="s">
+        <v>358</v>
+      </c>
       <c r="F7" t="s">
         <v>24</v>
       </c>
@@ -3582,9 +4032,10 @@
       <c r="K7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="26" t="s">
+      <c r="L7" s="2" t="s">
         <v>337</v>
       </c>
+      <c r="M7" s="33"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -3596,6 +4047,9 @@
       <c r="C8" s="18" t="s">
         <v>256</v>
       </c>
+      <c r="D8" s="15" t="s">
+        <v>359</v>
+      </c>
       <c r="F8" t="s">
         <v>28</v>
       </c>
@@ -3614,7 +4068,9 @@
       <c r="L8" t="s">
         <v>333</v>
       </c>
-      <c r="M8" s="18"/>
+      <c r="M8" s="33" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -3627,7 +4083,7 @@
         <v>253</v>
       </c>
       <c r="D9" t="s">
-        <v>354</v>
+        <v>493</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>32</v>
@@ -3647,7 +4103,7 @@
       <c r="L9" t="s">
         <v>274</v>
       </c>
-      <c r="M9" s="18"/>
+      <c r="M9" s="33"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -3659,6 +4115,9 @@
       <c r="C10" s="18" t="s">
         <v>257</v>
       </c>
+      <c r="D10" s="15" t="s">
+        <v>500</v>
+      </c>
       <c r="F10" t="s">
         <v>36</v>
       </c>
@@ -3674,9 +4133,10 @@
       <c r="K10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="26" t="s">
         <v>325</v>
       </c>
+      <c r="M10" s="33"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -3688,6 +4148,9 @@
       <c r="C11" s="19" t="s">
         <v>258</v>
       </c>
+      <c r="D11" s="15" t="s">
+        <v>492</v>
+      </c>
       <c r="F11" t="s">
         <v>40</v>
       </c>
@@ -3706,7 +4169,9 @@
       <c r="L11" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="M11" s="18"/>
+      <c r="M11" s="33" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -3718,6 +4183,9 @@
       <c r="C12" s="18" t="s">
         <v>259</v>
       </c>
+      <c r="D12" s="15" t="s">
+        <v>496</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>43</v>
       </c>
@@ -3736,7 +4204,9 @@
       <c r="L12" t="s">
         <v>259</v>
       </c>
-      <c r="M12" s="18"/>
+      <c r="M12" s="33" t="s">
+        <v>496</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -3748,6 +4218,9 @@
       <c r="C13" s="18" t="s">
         <v>260</v>
       </c>
+      <c r="D13" t="s">
+        <v>494</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>47</v>
       </c>
@@ -3766,7 +4239,7 @@
       <c r="L13" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="M13" s="14"/>
+      <c r="M13" s="33"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -3778,6 +4251,9 @@
       <c r="C14" s="18" t="s">
         <v>284</v>
       </c>
+      <c r="D14" t="s">
+        <v>487</v>
+      </c>
       <c r="F14" t="s">
         <v>51</v>
       </c>
@@ -3796,7 +4272,7 @@
       <c r="L14" t="s">
         <v>336</v>
       </c>
-      <c r="M14" s="18"/>
+      <c r="M14" s="33"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -3808,6 +4284,9 @@
       <c r="C15" s="25" t="s">
         <v>261</v>
       </c>
+      <c r="D15" t="s">
+        <v>495</v>
+      </c>
       <c r="F15" t="s">
         <v>54</v>
       </c>
@@ -3826,6 +4305,7 @@
       <c r="L15" s="2" t="s">
         <v>337</v>
       </c>
+      <c r="M15" s="33"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -3837,6 +4317,9 @@
       <c r="C16" s="18" t="s">
         <v>262</v>
       </c>
+      <c r="D16" t="s">
+        <v>499</v>
+      </c>
       <c r="F16" t="s">
         <v>57</v>
       </c>
@@ -3855,7 +4338,7 @@
       <c r="L16" t="s">
         <v>262</v>
       </c>
-      <c r="M16" s="18"/>
+      <c r="M16" s="33"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -3868,7 +4351,7 @@
         <v>277</v>
       </c>
       <c r="D17" t="s">
-        <v>357</v>
+        <v>503</v>
       </c>
       <c r="F17" t="s">
         <v>61</v>
@@ -3888,6 +4371,7 @@
       <c r="L17" t="s">
         <v>337</v>
       </c>
+      <c r="M17" s="33"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -3899,6 +4383,9 @@
       <c r="C18" s="20" t="s">
         <v>263</v>
       </c>
+      <c r="D18" t="s">
+        <v>489</v>
+      </c>
       <c r="F18" t="s">
         <v>65</v>
       </c>
@@ -3917,7 +4404,7 @@
       <c r="L18" t="s">
         <v>337</v>
       </c>
-      <c r="M18" s="18"/>
+      <c r="M18" s="33"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -3929,6 +4416,9 @@
       <c r="C19" s="20" t="s">
         <v>351</v>
       </c>
+      <c r="D19" t="s">
+        <v>490</v>
+      </c>
       <c r="F19" t="s">
         <v>69</v>
       </c>
@@ -3947,7 +4437,7 @@
       <c r="L19" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="M19" s="18"/>
+      <c r="M19" s="33"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -3960,7 +4450,7 @@
         <v>264</v>
       </c>
       <c r="D20" t="s">
-        <v>355</v>
+        <v>491</v>
       </c>
       <c r="F20" t="s">
         <v>73</v>
@@ -3980,9 +4470,7 @@
       <c r="L20" t="s">
         <v>271</v>
       </c>
-      <c r="M20" t="s">
-        <v>356</v>
-      </c>
+      <c r="M20" s="33"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -3994,6 +4482,9 @@
       <c r="C21" s="19" t="s">
         <v>265</v>
       </c>
+      <c r="D21" t="s">
+        <v>488</v>
+      </c>
       <c r="F21" s="1" t="s">
         <v>77</v>
       </c>
@@ -4012,7 +4503,7 @@
       <c r="L21" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="M21" s="18"/>
+      <c r="M21" s="33"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -4024,6 +4515,9 @@
       <c r="C22" s="18" t="s">
         <v>284</v>
       </c>
+      <c r="D22" t="s">
+        <v>498</v>
+      </c>
       <c r="F22" t="s">
         <v>80</v>
       </c>
@@ -4042,7 +4536,7 @@
       <c r="L22" t="s">
         <v>336</v>
       </c>
-      <c r="M22" s="18"/>
+      <c r="M22" s="33"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -4054,6 +4548,9 @@
       <c r="C23" s="25" t="s">
         <v>261</v>
       </c>
+      <c r="D23" t="s">
+        <v>502</v>
+      </c>
       <c r="F23" t="s">
         <v>83</v>
       </c>
@@ -4072,7 +4569,7 @@
       <c r="L23" s="29" t="s">
         <v>361</v>
       </c>
-      <c r="M23" s="18"/>
+      <c r="M23" s="33"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -4084,6 +4581,9 @@
       <c r="C24" s="21" t="s">
         <v>266</v>
       </c>
+      <c r="D24" t="s">
+        <v>504</v>
+      </c>
       <c r="F24" t="s">
         <v>87</v>
       </c>
@@ -4102,7 +4602,7 @@
       <c r="L24" s="14" t="s">
         <v>342</v>
       </c>
-      <c r="M24" s="14"/>
+      <c r="M24" s="33"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -4114,6 +4614,9 @@
       <c r="C25" s="18" t="s">
         <v>267</v>
       </c>
+      <c r="D25" t="s">
+        <v>497</v>
+      </c>
       <c r="F25" t="s">
         <v>91</v>
       </c>
@@ -4132,7 +4635,7 @@
       <c r="L25" t="s">
         <v>267</v>
       </c>
-      <c r="M25" s="18"/>
+      <c r="M25" s="33"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -4144,6 +4647,9 @@
       <c r="C26" s="18" t="s">
         <v>253</v>
       </c>
+      <c r="D26" t="s">
+        <v>505</v>
+      </c>
       <c r="F26" t="s">
         <v>94</v>
       </c>
@@ -4162,7 +4668,7 @@
       <c r="L26" t="s">
         <v>253</v>
       </c>
-      <c r="M26" s="18"/>
+      <c r="M26" s="33"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -4174,6 +4680,9 @@
       <c r="C27" s="19" t="s">
         <v>268</v>
       </c>
+      <c r="D27" t="s">
+        <v>506</v>
+      </c>
       <c r="F27" s="1" t="s">
         <v>97</v>
       </c>
@@ -4192,7 +4701,7 @@
       <c r="L27" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="M27" s="18"/>
+      <c r="M27" s="33"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -4204,6 +4713,9 @@
       <c r="C28" s="18" t="s">
         <v>269</v>
       </c>
+      <c r="D28" t="s">
+        <v>507</v>
+      </c>
       <c r="F28" t="s">
         <v>100</v>
       </c>
@@ -4222,7 +4734,7 @@
       <c r="L28" t="s">
         <v>269</v>
       </c>
-      <c r="M28" s="18"/>
+      <c r="M28" s="33"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -4234,6 +4746,9 @@
       <c r="C29" s="18" t="s">
         <v>270</v>
       </c>
+      <c r="D29" t="s">
+        <v>508</v>
+      </c>
       <c r="F29" t="s">
         <v>103</v>
       </c>
@@ -4250,9 +4765,9 @@
         <v>105</v>
       </c>
       <c r="L29" t="s">
-        <v>378</v>
-      </c>
-      <c r="M29" s="18"/>
+        <v>373</v>
+      </c>
+      <c r="M29" s="33"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -4265,7 +4780,7 @@
         <v>271</v>
       </c>
       <c r="D30" t="s">
-        <v>356</v>
+        <v>511</v>
       </c>
       <c r="F30" t="s">
         <v>106</v>
@@ -4285,9 +4800,7 @@
       <c r="L30" t="s">
         <v>264</v>
       </c>
-      <c r="M30" t="s">
-        <v>355</v>
-      </c>
+      <c r="M30" s="33"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -4299,6 +4812,9 @@
       <c r="C31" t="s">
         <v>270</v>
       </c>
+      <c r="D31" t="s">
+        <v>512</v>
+      </c>
       <c r="F31" t="s">
         <v>110</v>
       </c>
@@ -4317,7 +4833,7 @@
       <c r="L31" t="s">
         <v>259</v>
       </c>
-      <c r="M31" t="s">
+      <c r="M31" s="33" t="s">
         <v>352</v>
       </c>
     </row>
@@ -4331,6 +4847,9 @@
       <c r="C32" s="20" t="s">
         <v>274</v>
       </c>
+      <c r="D32" t="s">
+        <v>513</v>
+      </c>
       <c r="F32" t="s">
         <v>114</v>
       </c>
@@ -4349,6 +4868,7 @@
       <c r="L32" t="s">
         <v>337</v>
       </c>
+      <c r="M32" s="33"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
@@ -4360,6 +4880,9 @@
       <c r="C33" s="20" t="s">
         <v>267</v>
       </c>
+      <c r="D33" t="s">
+        <v>514</v>
+      </c>
       <c r="F33" t="s">
         <v>117</v>
       </c>
@@ -4378,7 +4901,7 @@
       <c r="L33" t="s">
         <v>267</v>
       </c>
-      <c r="M33" s="18"/>
+      <c r="M33" s="33"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -4390,6 +4913,9 @@
       <c r="C34" s="19" t="s">
         <v>272</v>
       </c>
+      <c r="D34" t="s">
+        <v>515</v>
+      </c>
       <c r="F34" t="s">
         <v>121</v>
       </c>
@@ -4408,7 +4934,7 @@
       <c r="L34" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="M34" s="18"/>
+      <c r="M34" s="33"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -4420,6 +4946,9 @@
       <c r="C35" s="18" t="s">
         <v>283</v>
       </c>
+      <c r="D35" t="s">
+        <v>509</v>
+      </c>
       <c r="F35" s="1" t="s">
         <v>124</v>
       </c>
@@ -4438,7 +4967,7 @@
       <c r="L35" t="s">
         <v>283</v>
       </c>
-      <c r="M35" s="18"/>
+      <c r="M35" s="33"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -4450,6 +4979,9 @@
       <c r="C36" s="18" t="s">
         <v>253</v>
       </c>
+      <c r="D36" t="s">
+        <v>516</v>
+      </c>
       <c r="F36" t="s">
         <v>128</v>
       </c>
@@ -4468,7 +5000,7 @@
       <c r="L36" t="s">
         <v>253</v>
       </c>
-      <c r="M36" s="18"/>
+      <c r="M36" s="33"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -4480,6 +5012,9 @@
       <c r="C37" s="20" t="s">
         <v>274</v>
       </c>
+      <c r="D37" t="s">
+        <v>517</v>
+      </c>
       <c r="F37" t="s">
         <v>132</v>
       </c>
@@ -4498,9 +5033,7 @@
       <c r="L37" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="M37" t="s">
-        <v>354</v>
-      </c>
+      <c r="M37" s="33"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -4512,6 +5045,9 @@
       <c r="C38" s="19" t="s">
         <v>273</v>
       </c>
+      <c r="D38" t="s">
+        <v>518</v>
+      </c>
       <c r="F38" t="s">
         <v>136</v>
       </c>
@@ -4530,7 +5066,7 @@
       <c r="L38" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="M38" s="18"/>
+      <c r="M38" s="33"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -4542,6 +5078,9 @@
       <c r="C39" s="18" t="s">
         <v>262</v>
       </c>
+      <c r="D39" t="s">
+        <v>501</v>
+      </c>
       <c r="F39" t="s">
         <v>139</v>
       </c>
@@ -4558,9 +5097,9 @@
         <v>141</v>
       </c>
       <c r="L39" t="s">
-        <v>262</v>
-      </c>
-      <c r="M39" s="18"/>
+        <v>529</v>
+      </c>
+      <c r="M39" s="33"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -4573,7 +5112,7 @@
         <v>274</v>
       </c>
       <c r="D40" t="s">
-        <v>358</v>
+        <v>519</v>
       </c>
       <c r="F40" t="s">
         <v>142</v>
@@ -4590,12 +5129,10 @@
       <c r="K40" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L40" s="26" t="s">
+      <c r="L40" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="M40" t="s">
-        <v>358</v>
-      </c>
+      <c r="M40" s="33"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -4607,6 +5144,9 @@
       <c r="C41" s="25" t="s">
         <v>275</v>
       </c>
+      <c r="D41" t="s">
+        <v>520</v>
+      </c>
       <c r="F41" t="s">
         <v>146</v>
       </c>
@@ -4625,7 +5165,7 @@
       <c r="L41" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="M41" s="14"/>
+      <c r="M41" s="33"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -4637,6 +5177,9 @@
       <c r="C42" s="18" t="s">
         <v>276</v>
       </c>
+      <c r="D42" t="s">
+        <v>521</v>
+      </c>
       <c r="F42" t="s">
         <v>150</v>
       </c>
@@ -4655,7 +5198,7 @@
       <c r="L42" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="M42" s="18"/>
+      <c r="M42" s="33"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -4667,6 +5210,9 @@
       <c r="C43" s="15" t="s">
         <v>277</v>
       </c>
+      <c r="D43" t="s">
+        <v>522</v>
+      </c>
       <c r="F43" s="1" t="s">
         <v>153</v>
       </c>
@@ -4683,9 +5229,9 @@
         <v>156</v>
       </c>
       <c r="L43" s="27" t="s">
-        <v>388</v>
-      </c>
-      <c r="M43" s="18"/>
+        <v>383</v>
+      </c>
+      <c r="M43" s="33"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -4697,6 +5243,9 @@
       <c r="C44" s="18" t="s">
         <v>256</v>
       </c>
+      <c r="D44" t="s">
+        <v>523</v>
+      </c>
       <c r="F44" t="s">
         <v>157</v>
       </c>
@@ -4715,7 +5264,7 @@
       <c r="L44" t="s">
         <v>346</v>
       </c>
-      <c r="M44" s="18"/>
+      <c r="M44" s="33"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -4727,6 +5276,9 @@
       <c r="C45" s="18" t="s">
         <v>278</v>
       </c>
+      <c r="D45" t="s">
+        <v>510</v>
+      </c>
       <c r="F45" t="s">
         <v>160</v>
       </c>
@@ -4745,7 +5297,7 @@
       <c r="L45" t="s">
         <v>278</v>
       </c>
-      <c r="M45" s="18"/>
+      <c r="M45" s="33"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
@@ -4757,6 +5309,9 @@
       <c r="C46" s="21" t="s">
         <v>279</v>
       </c>
+      <c r="D46" t="s">
+        <v>524</v>
+      </c>
       <c r="F46" t="s">
         <v>164</v>
       </c>
@@ -4770,12 +5325,14 @@
         <v>164</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="L46" t="s">
         <v>347</v>
       </c>
-      <c r="M46" s="18"/>
+      <c r="M46" s="33" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
@@ -4788,7 +5345,7 @@
         <v>277</v>
       </c>
       <c r="D47" t="s">
-        <v>353</v>
+        <v>525</v>
       </c>
       <c r="F47" t="s">
         <v>168</v>
@@ -4808,6 +5365,7 @@
       <c r="L47" t="s">
         <v>337</v>
       </c>
+      <c r="M47" s="33"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -4819,6 +5377,9 @@
       <c r="C48" s="18" t="s">
         <v>260</v>
       </c>
+      <c r="D48" t="s">
+        <v>526</v>
+      </c>
       <c r="F48" t="s">
         <v>172</v>
       </c>
@@ -4837,6 +5398,7 @@
       <c r="L48" t="s">
         <v>337</v>
       </c>
+      <c r="M48" s="33"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -4848,6 +5410,9 @@
       <c r="C49" s="18" t="s">
         <v>260</v>
       </c>
+      <c r="D49" t="s">
+        <v>527</v>
+      </c>
       <c r="F49" s="1" t="s">
         <v>176</v>
       </c>
@@ -4866,6 +5431,7 @@
       <c r="L49" t="s">
         <v>337</v>
       </c>
+      <c r="M49" s="33"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -4877,6 +5443,9 @@
       <c r="C50" s="25" t="s">
         <v>261</v>
       </c>
+      <c r="D50" t="s">
+        <v>528</v>
+      </c>
       <c r="F50" s="1" t="s">
         <v>180</v>
       </c>
@@ -4895,6 +5464,7 @@
       <c r="L50" t="s">
         <v>337</v>
       </c>
+      <c r="M50" s="33"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J51" s="3" t="s">
@@ -4903,9 +5473,10 @@
       <c r="K51" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="L51" s="26" t="s">
+      <c r="L51" s="2" t="s">
         <v>274</v>
       </c>
+      <c r="M51" s="33"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -4935,9 +5506,7 @@
       <c r="L52" t="s">
         <v>277</v>
       </c>
-      <c r="M52" t="s">
-        <v>353</v>
-      </c>
+      <c r="M52" s="33"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -4996,7 +5565,9 @@
       <c r="L54" t="s">
         <v>254</v>
       </c>
-      <c r="M54" s="18"/>
+      <c r="M54" s="33" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -5021,11 +5592,12 @@
         <v>192</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>193</v>
+        <v>486</v>
       </c>
       <c r="L55" t="s">
         <v>348</v>
       </c>
+      <c r="M55" s="33"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
@@ -5053,8 +5625,9 @@
         <v>195</v>
       </c>
       <c r="L56" s="26" t="s">
-        <v>389</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="M56" s="33"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F57" t="s">
@@ -5075,7 +5648,9 @@
       <c r="L57" t="s">
         <v>347</v>
       </c>
-      <c r="M57" s="18"/>
+      <c r="M57" s="33" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F58" t="s">
@@ -5096,7 +5671,9 @@
       <c r="L58" t="s">
         <v>347</v>
       </c>
-      <c r="M58" s="18"/>
+      <c r="M58" s="33" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J59" s="3" t="s">
@@ -5106,8 +5683,9 @@
         <v>201</v>
       </c>
       <c r="L59" s="26" t="s">
-        <v>370</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="M59" s="33"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J60" s="3" t="s">
@@ -5117,9 +5695,9 @@
         <v>251</v>
       </c>
       <c r="L60" s="26" t="s">
-        <v>377</v>
-      </c>
-      <c r="M60" s="18"/>
+        <v>372</v>
+      </c>
+      <c r="M60" s="33"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J61" t="s">
@@ -5128,20 +5706,22 @@
       <c r="K61" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="L61" s="26" t="s">
-        <v>373</v>
-      </c>
+      <c r="L61" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="M61" s="33"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J62" s="3" t="s">
         <v>206</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="L62" s="15" t="s">
-        <v>396</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="L62" t="s">
+        <v>530</v>
+      </c>
+      <c r="M62" s="33"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J63" t="s">
@@ -5153,9 +5733,7 @@
       <c r="L63" t="s">
         <v>277</v>
       </c>
-      <c r="M63" t="s">
-        <v>357</v>
-      </c>
+      <c r="M63" s="33"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J64" t="s">
@@ -5165,8 +5743,9 @@
         <v>211</v>
       </c>
       <c r="L64" s="26" t="s">
-        <v>376</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="M64" s="33"/>
     </row>
     <row r="65" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J65" s="3" t="s">
@@ -5175,9 +5754,10 @@
       <c r="K65" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="L65" s="26" t="s">
-        <v>369</v>
-      </c>
+      <c r="L65" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="M65" s="33"/>
     </row>
     <row r="66" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J66" t="s">
@@ -5186,9 +5766,10 @@
       <c r="K66" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="L66" s="26" t="s">
-        <v>347</v>
-      </c>
+      <c r="L66" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="M66" s="33"/>
     </row>
     <row r="67" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J67" t="s">
@@ -5198,8 +5779,9 @@
         <v>217</v>
       </c>
       <c r="L67" t="s">
-        <v>368</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="M67" s="33"/>
     </row>
     <row r="68" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J68" s="3" t="s">
@@ -5208,21 +5790,22 @@
       <c r="K68" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="L68" s="26" t="s">
+      <c r="L68" s="2" t="s">
         <v>337</v>
       </c>
+      <c r="M68" s="33"/>
     </row>
     <row r="69" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H69" s="33"/>
       <c r="J69" t="s">
         <v>220</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="L69" s="26" t="s">
-        <v>372</v>
-      </c>
+      <c r="L69" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="M69" s="33"/>
     </row>
     <row r="70" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J70" t="s">
@@ -5234,6 +5817,7 @@
       <c r="L70" s="29" t="s">
         <v>362</v>
       </c>
+      <c r="M70" s="33"/>
     </row>
     <row r="71" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J71" s="3" t="s">
@@ -5245,8 +5829,12 @@
       <c r="L71" s="26" t="s">
         <v>303</v>
       </c>
+      <c r="M71" s="33"/>
     </row>
     <row r="72" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H72" s="15" t="s">
+        <v>535</v>
+      </c>
       <c r="J72" t="s">
         <v>224</v>
       </c>
@@ -5256,6 +5844,7 @@
       <c r="L72" s="29" t="s">
         <v>364</v>
       </c>
+      <c r="M72" s="33"/>
     </row>
     <row r="73" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J73" t="s">
@@ -5267,6 +5856,7 @@
       <c r="L73" s="29" t="s">
         <v>363</v>
       </c>
+      <c r="M73" s="33"/>
     </row>
     <row r="74" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J74" s="3" t="s">
@@ -5275,9 +5865,10 @@
       <c r="K74" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="L74" s="26" t="s">
-        <v>374</v>
-      </c>
+      <c r="L74" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="M74" s="33"/>
     </row>
     <row r="75" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J75" t="s">
@@ -5289,7 +5880,9 @@
       <c r="L75" t="s">
         <v>253</v>
       </c>
-      <c r="M75" s="18"/>
+      <c r="M75" s="33" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="76" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J76" t="s">
@@ -5301,7 +5894,7 @@
       <c r="L76" t="s">
         <v>349</v>
       </c>
-      <c r="M76" s="18"/>
+      <c r="M76" s="33"/>
     </row>
     <row r="77" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J77" t="s">
@@ -5313,7 +5906,7 @@
       <c r="L77" t="s">
         <v>349</v>
       </c>
-      <c r="M77" s="18"/>
+      <c r="M77" s="33"/>
     </row>
     <row r="78" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J78" t="s">
@@ -5325,7 +5918,7 @@
       <c r="L78" t="s">
         <v>349</v>
       </c>
-      <c r="M78" s="18"/>
+      <c r="M78" s="33"/>
     </row>
     <row r="79" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J79" s="3" t="s">
@@ -5335,8 +5928,9 @@
         <v>237</v>
       </c>
       <c r="L79" s="26" t="s">
-        <v>371</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="M79" s="33"/>
     </row>
     <row r="80" spans="8:13" x14ac:dyDescent="0.25">
       <c r="J80" t="s">
@@ -5348,6 +5942,7 @@
       <c r="L80" s="29" t="s">
         <v>365</v>
       </c>
+      <c r="M80" s="33"/>
     </row>
     <row r="81" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J81" s="3" t="s">
@@ -5359,6 +5954,7 @@
       <c r="L81" s="29" t="s">
         <v>367</v>
       </c>
+      <c r="M81" s="33"/>
     </row>
     <row r="82" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J82" t="s">
@@ -5370,6 +5966,7 @@
       <c r="L82" s="29" t="s">
         <v>366</v>
       </c>
+      <c r="M82" s="33"/>
     </row>
     <row r="83" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J83" t="s">
@@ -5378,9 +5975,10 @@
       <c r="K83" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="L83" s="15" t="s">
+      <c r="L83" s="34" t="s">
         <v>330</v>
       </c>
+      <c r="M83" s="33"/>
     </row>
     <row r="84" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J84" s="3" t="s">
@@ -5389,10 +5987,10 @@
       <c r="K84" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="L84" s="26" t="s">
-        <v>375</v>
-      </c>
-      <c r="M84" s="18"/>
+      <c r="L84" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="M84" s="33"/>
     </row>
     <row r="85" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J85" s="3" t="s">
@@ -5405,29 +6003,31 @@
     <row r="87" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G87" s="7"/>
       <c r="J87" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="L87" t="s">
         <v>275</v>
       </c>
+      <c r="M87" s="33"/>
     </row>
     <row r="88" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J88" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="L88" t="s">
         <v>276</v>
       </c>
+      <c r="M88" s="33"/>
     </row>
     <row r="89" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J89" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>152</v>
@@ -5435,82 +6035,91 @@
       <c r="L89" t="s">
         <v>276</v>
       </c>
+      <c r="M89" s="33"/>
     </row>
     <row r="90" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J90" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="L90" t="s">
         <v>276</v>
       </c>
+      <c r="M90" s="33"/>
     </row>
     <row r="91" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J91" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="L91" t="s">
         <v>276</v>
       </c>
+      <c r="M91" s="33"/>
     </row>
     <row r="92" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J92" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
+      </c>
+      <c r="L92" s="26" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="93" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J93" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="L93" t="s">
-        <v>391</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="M93" s="33"/>
     </row>
     <row r="94" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J94" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="L94" t="s">
-        <v>391</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="M94" s="33"/>
     </row>
     <row r="95" spans="7:13" x14ac:dyDescent="0.25">
       <c r="J95" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="L95" t="s">
-        <v>391</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="M95" s="33"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G59 G61:G62 G64:G65 G67:G68 F66 G70:G1048576 B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K61 K63:K84 K87:K88 K97:K1048576 K90:K95">
+    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
     <cfRule type="duplicateValues" dxfId="5" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K61 K63:K84 K87:K88 K97:K1048576 K90:K95">
-    <cfRule type="duplicateValues" dxfId="4" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5529,15 +6138,15 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5545,490 +6154,1066 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567A5AB6-FEDF-4372-B229-114F8DE27E46}">
-  <dimension ref="A2:A95"/>
+  <dimension ref="A3:D119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="2" customWidth="1"/>
+    <col min="1" max="2" width="16.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="D10" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D11" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="D12" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D15" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D17" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B18" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D18" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="B21" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D21" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="B22" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D23" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="B24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="B25" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="D25" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="B27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="B31" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D31" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D32" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="B33" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="D33" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="B34" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D34" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="B35" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="B36" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D36" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="B37" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D37" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="B38" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="B39" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D39" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="17" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="B40" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D40" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+      <c r="B41" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="D41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="B42" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D42" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="16" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="B43" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="17" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="B44" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="28" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="B45" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D45" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="B46" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D47" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D48" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+      <c r="B49" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D49" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="B50" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="B51" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D51" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+      <c r="B52" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D52" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="B53" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D53" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+      <c r="B54" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D54" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+      <c r="B55" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D55" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+      <c r="B56" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D56" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
+      <c r="B57" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D57" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
+      <c r="B58" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D58" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
+      <c r="B59" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D59" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+      <c r="B60" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="D60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+      <c r="B61" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D61" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D62" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
+      <c r="B63" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D63" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D64" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
+      <c r="B71" s="17" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B75" s="17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B79" s="17" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B91" s="17" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B92" s="17" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A69 A71:A88 A111:A1048576 A90:A96">
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E1:E148">
+    <sortCondition ref="E58:E148"/>
+  </sortState>
+  <conditionalFormatting sqref="A98:A119">
+    <cfRule type="duplicateValues" dxfId="3" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:C1 A25:C1048576 A2:B24">
+  <conditionalFormatting sqref="D1:D2 D65:D1048576 B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576 B1:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G44">
+  <conditionalFormatting sqref="E63:E1048576 D3:D64">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
